--- a/artfynd/A 26012-2024 artfynd.xlsx
+++ b/artfynd/A 26012-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131328398</v>
       </c>
       <c r="B2" t="n">
-        <v>92111</v>
+        <v>92112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131328384</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131328402</v>
+        <v>131328390</v>
       </c>
       <c r="B4" t="n">
         <v>57884</v>
@@ -925,12 +925,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -940,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560775</v>
+        <v>560915</v>
       </c>
       <c r="R4" t="n">
-        <v>6913519</v>
+        <v>6913505</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -985,12 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131328390</v>
+        <v>131328402</v>
       </c>
       <c r="B5" t="n">
         <v>57884</v>
@@ -1045,20 +1048,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1068,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560915</v>
+        <v>560775</v>
       </c>
       <c r="R5" t="n">
-        <v>6913505</v>
+        <v>6913519</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1113,7 +1108,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131328388</v>
+        <v>131328399</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>91834</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,42 +1271,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560937</v>
+        <v>560809</v>
       </c>
       <c r="R7" t="n">
-        <v>6913518</v>
+        <v>6913541</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,7 +1326,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,12 +1336,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Påtagligt äldre bohål av sannolikt tretåig hackspett. Hålet sitter i en död gran omkring 1,5 meter ovan mark och innerdiametern är 4,5 cm. I området finns ett stort antal barrträd med ringhack i en för arten lämplig biotop.</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131328399</v>
+        <v>131328388</v>
       </c>
       <c r="B8" t="n">
-        <v>91833</v>
+        <v>57884</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1391,30 +1374,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560809</v>
+        <v>560937</v>
       </c>
       <c r="R8" t="n">
-        <v>6913541</v>
+        <v>6913518</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1446,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1451,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påtagligt äldre bohål av sannolikt tretåig hackspett. Hålet sitter i en död gran omkring 1,5 meter ovan mark och innerdiametern är 4,5 cm. I området finns ett stort antal barrträd med ringhack i en för arten lämplig biotop.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,7 +1486,7 @@
         <v>131328396</v>
       </c>
       <c r="B9" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131328394</v>
+        <v>131328393</v>
       </c>
       <c r="B10" t="n">
         <v>57884</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560867</v>
+        <v>560855</v>
       </c>
       <c r="R10" t="n">
-        <v>6913516</v>
+        <v>6913506</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1710,7 +1710,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131328393</v>
+        <v>131328394</v>
       </c>
       <c r="B11" t="n">
         <v>57884</v>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>560855</v>
+        <v>560867</v>
       </c>
       <c r="R11" t="n">
-        <v>6913506</v>
+        <v>6913516</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1833,7 +1833,7 @@
         <v>131328397</v>
       </c>
       <c r="B12" t="n">
-        <v>92272</v>
+        <v>92273</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>131328389</v>
       </c>
       <c r="B14" t="n">
-        <v>92111</v>
+        <v>92112</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131328395</v>
+        <v>131328386</v>
       </c>
       <c r="B16" t="n">
         <v>57884</v>
@@ -2327,10 +2327,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560835</v>
+        <v>560936</v>
       </c>
       <c r="R16" t="n">
-        <v>6913527</v>
+        <v>6913562</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2404,7 +2404,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131328391</v>
+        <v>131328395</v>
       </c>
       <c r="B17" t="n">
         <v>57884</v>
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560893</v>
+        <v>560835</v>
       </c>
       <c r="R17" t="n">
-        <v>6913550</v>
+        <v>6913527</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2492,12 +2492,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2524,7 +2524,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131328386</v>
+        <v>131328391</v>
       </c>
       <c r="B18" t="n">
         <v>57884</v>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560936</v>
+        <v>560893</v>
       </c>
       <c r="R18" t="n">
-        <v>6913562</v>
+        <v>6913550</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2612,12 +2612,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2767,7 +2767,7 @@
         <v>131328385</v>
       </c>
       <c r="B20" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 26012-2024 artfynd.xlsx
+++ b/artfynd/A 26012-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131328398</v>
       </c>
       <c r="B2" t="n">
-        <v>92112</v>
+        <v>92114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131328384</v>
       </c>
       <c r="B3" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>131328390</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>131328402</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>131328387</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>131328399</v>
       </c>
       <c r="B7" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>131328388</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>131328396</v>
       </c>
       <c r="B9" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>131328393</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>131328394</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>131328397</v>
       </c>
       <c r="B12" t="n">
-        <v>92273</v>
+        <v>92275</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>131328401</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>131328389</v>
       </c>
       <c r="B14" t="n">
-        <v>92112</v>
+        <v>92114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>131328400</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>131328386</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>131328395</v>
       </c>
       <c r="B17" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>131328391</v>
       </c>
       <c r="B18" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>131328392</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>131328385</v>
       </c>
       <c r="B20" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 26012-2024 artfynd.xlsx
+++ b/artfynd/A 26012-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131328398</v>
       </c>
       <c r="B2" t="n">
-        <v>92114</v>
+        <v>92115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131328384</v>
       </c>
       <c r="B3" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>131328390</v>
       </c>
       <c r="B4" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>131328402</v>
       </c>
       <c r="B5" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>131328387</v>
       </c>
       <c r="B6" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>131328399</v>
       </c>
       <c r="B7" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>131328388</v>
       </c>
       <c r="B8" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>131328396</v>
       </c>
       <c r="B9" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>131328393</v>
       </c>
       <c r="B10" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>131328394</v>
       </c>
       <c r="B11" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>131328397</v>
       </c>
       <c r="B12" t="n">
-        <v>92275</v>
+        <v>92276</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>131328401</v>
       </c>
       <c r="B13" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>131328389</v>
       </c>
       <c r="B14" t="n">
-        <v>92114</v>
+        <v>92115</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>131328400</v>
       </c>
       <c r="B15" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>131328386</v>
       </c>
       <c r="B16" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>131328395</v>
       </c>
       <c r="B17" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>131328391</v>
       </c>
       <c r="B18" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>131328392</v>
       </c>
       <c r="B19" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>131328385</v>
       </c>
       <c r="B20" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 26012-2024 artfynd.xlsx
+++ b/artfynd/A 26012-2024 artfynd.xlsx
@@ -2284,7 +2284,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131328386</v>
+        <v>131328395</v>
       </c>
       <c r="B16" t="n">
         <v>57887</v>
@@ -2327,10 +2327,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560936</v>
+        <v>560835</v>
       </c>
       <c r="R16" t="n">
-        <v>6913562</v>
+        <v>6913527</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2404,7 +2404,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131328395</v>
+        <v>131328391</v>
       </c>
       <c r="B17" t="n">
         <v>57887</v>
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560835</v>
+        <v>560893</v>
       </c>
       <c r="R17" t="n">
-        <v>6913527</v>
+        <v>6913550</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2492,12 +2492,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2524,7 +2524,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131328391</v>
+        <v>131328386</v>
       </c>
       <c r="B18" t="n">
         <v>57887</v>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560893</v>
+        <v>560936</v>
       </c>
       <c r="R18" t="n">
-        <v>6913550</v>
+        <v>6913562</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2612,12 +2612,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 26012-2024 artfynd.xlsx
+++ b/artfynd/A 26012-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131328398</v>
       </c>
       <c r="B2" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131328384</v>
       </c>
       <c r="B3" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>131328390</v>
       </c>
       <c r="B4" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>131328402</v>
       </c>
       <c r="B5" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>131328387</v>
       </c>
       <c r="B6" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131328388</v>
+        <v>131328399</v>
       </c>
       <c r="B7" t="n">
-        <v>57892</v>
+        <v>91848</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,42 +1271,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560937</v>
+        <v>560809</v>
       </c>
       <c r="R7" t="n">
-        <v>6913518</v>
+        <v>6913541</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,7 +1326,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,12 +1336,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Påtagligt äldre bohål av sannolikt tretåig hackspett. Hålet sitter i en död gran omkring 1,5 meter ovan mark och innerdiametern är 4,5 cm. I området finns ett stort antal barrträd med ringhack i en för arten lämplig biotop.</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131328399</v>
+        <v>131328388</v>
       </c>
       <c r="B8" t="n">
-        <v>91842</v>
+        <v>57898</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1391,30 +1374,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560809</v>
+        <v>560937</v>
       </c>
       <c r="R8" t="n">
-        <v>6913541</v>
+        <v>6913518</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1446,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1451,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påtagligt äldre bohål av sannolikt tretåig hackspett. Hålet sitter i en död gran omkring 1,5 meter ovan mark och innerdiametern är 4,5 cm. I området finns ett stort antal barrträd med ringhack i en för arten lämplig biotop.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,7 +1486,7 @@
         <v>131328396</v>
       </c>
       <c r="B9" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>131328393</v>
       </c>
       <c r="B10" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>131328394</v>
       </c>
       <c r="B11" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>131328397</v>
       </c>
       <c r="B12" t="n">
-        <v>92281</v>
+        <v>92287</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>131328401</v>
       </c>
       <c r="B13" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>131328389</v>
       </c>
       <c r="B14" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>131328400</v>
       </c>
       <c r="B15" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>131328386</v>
       </c>
       <c r="B16" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>131328395</v>
       </c>
       <c r="B17" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>131328391</v>
       </c>
       <c r="B18" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>131328392</v>
       </c>
       <c r="B19" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>131328385</v>
       </c>
       <c r="B20" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 26012-2024 artfynd.xlsx
+++ b/artfynd/A 26012-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131328398</v>
       </c>
       <c r="B2" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131328399</v>
+        <v>131328388</v>
       </c>
       <c r="B7" t="n">
-        <v>91848</v>
+        <v>57898</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,30 +1271,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560809</v>
+        <v>560937</v>
       </c>
       <c r="R7" t="n">
-        <v>6913541</v>
+        <v>6913518</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1326,7 +1338,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1336,7 +1348,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påtagligt äldre bohål av sannolikt tretåig hackspett. Hålet sitter i en död gran omkring 1,5 meter ovan mark och innerdiametern är 4,5 cm. I området finns ett stort antal barrträd med ringhack i en för arten lämplig biotop.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,10 +1380,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131328388</v>
+        <v>131328399</v>
       </c>
       <c r="B8" t="n">
-        <v>57898</v>
+        <v>91848</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,42 +1391,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560937</v>
+        <v>560809</v>
       </c>
       <c r="R8" t="n">
-        <v>6913518</v>
+        <v>6913541</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,12 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Påtagligt äldre bohål av sannolikt tretåig hackspett. Hålet sitter i en död gran omkring 1,5 meter ovan mark och innerdiametern är 4,5 cm. I området finns ett stort antal barrträd med ringhack i en för arten lämplig biotop.</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1833,7 +1833,7 @@
         <v>131328397</v>
       </c>
       <c r="B12" t="n">
-        <v>92287</v>
+        <v>92288</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>131328389</v>
       </c>
       <c r="B14" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 26012-2024 artfynd.xlsx
+++ b/artfynd/A 26012-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131328398</v>
       </c>
       <c r="B2" t="n">
-        <v>92127</v>
+        <v>92128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131328384</v>
       </c>
       <c r="B3" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>131328390</v>
       </c>
       <c r="B4" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>131328402</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>131328387</v>
       </c>
       <c r="B6" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131328388</v>
+        <v>131328399</v>
       </c>
       <c r="B7" t="n">
-        <v>57898</v>
+        <v>91849</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,42 +1271,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560937</v>
+        <v>560809</v>
       </c>
       <c r="R7" t="n">
-        <v>6913518</v>
+        <v>6913541</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,7 +1326,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,12 +1336,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Påtagligt äldre bohål av sannolikt tretåig hackspett. Hålet sitter i en död gran omkring 1,5 meter ovan mark och innerdiametern är 4,5 cm. I området finns ett stort antal barrträd med ringhack i en för arten lämplig biotop.</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131328399</v>
+        <v>131328388</v>
       </c>
       <c r="B8" t="n">
-        <v>91848</v>
+        <v>57899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1391,30 +1374,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560809</v>
+        <v>560937</v>
       </c>
       <c r="R8" t="n">
-        <v>6913541</v>
+        <v>6913518</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1446,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1451,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påtagligt äldre bohål av sannolikt tretåig hackspett. Hålet sitter i en död gran omkring 1,5 meter ovan mark och innerdiametern är 4,5 cm. I området finns ett stort antal barrträd med ringhack i en för arten lämplig biotop.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,7 +1486,7 @@
         <v>131328396</v>
       </c>
       <c r="B9" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>131328393</v>
       </c>
       <c r="B10" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>131328394</v>
       </c>
       <c r="B11" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>131328397</v>
       </c>
       <c r="B12" t="n">
-        <v>92288</v>
+        <v>92289</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>131328401</v>
       </c>
       <c r="B13" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>131328389</v>
       </c>
       <c r="B14" t="n">
-        <v>92127</v>
+        <v>92128</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>131328400</v>
       </c>
       <c r="B15" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>131328386</v>
       </c>
       <c r="B16" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>131328395</v>
       </c>
       <c r="B17" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>131328391</v>
       </c>
       <c r="B18" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>131328392</v>
       </c>
       <c r="B19" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>131328385</v>
       </c>
       <c r="B20" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 26012-2024 artfynd.xlsx
+++ b/artfynd/A 26012-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131328398</v>
       </c>
       <c r="B2" t="n">
-        <v>92128</v>
+        <v>92131</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131328384</v>
       </c>
       <c r="B3" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>131328390</v>
       </c>
       <c r="B4" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>131328402</v>
       </c>
       <c r="B5" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>131328387</v>
       </c>
       <c r="B6" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>131328399</v>
       </c>
       <c r="B7" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>131328388</v>
       </c>
       <c r="B8" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>131328396</v>
       </c>
       <c r="B9" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>131328393</v>
       </c>
       <c r="B10" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>131328394</v>
       </c>
       <c r="B11" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>131328397</v>
       </c>
       <c r="B12" t="n">
-        <v>92289</v>
+        <v>92292</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>131328401</v>
       </c>
       <c r="B13" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>131328389</v>
       </c>
       <c r="B14" t="n">
-        <v>92128</v>
+        <v>92131</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>131328400</v>
       </c>
       <c r="B15" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>131328386</v>
       </c>
       <c r="B16" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>131328395</v>
       </c>
       <c r="B17" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>131328391</v>
       </c>
       <c r="B18" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>131328392</v>
       </c>
       <c r="B19" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>131328385</v>
       </c>
       <c r="B20" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 26012-2024 artfynd.xlsx
+++ b/artfynd/A 26012-2024 artfynd.xlsx
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131328390</v>
+        <v>131328402</v>
       </c>
       <c r="B4" t="n">
         <v>57902</v>
@@ -925,20 +925,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -948,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560915</v>
+        <v>560775</v>
       </c>
       <c r="R4" t="n">
-        <v>6913505</v>
+        <v>6913519</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +975,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +985,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,7 +1017,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131328402</v>
+        <v>131328390</v>
       </c>
       <c r="B5" t="n">
         <v>57902</v>
@@ -1048,12 +1045,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1063,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560775</v>
+        <v>560915</v>
       </c>
       <c r="R5" t="n">
-        <v>6913519</v>
+        <v>6913505</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1103,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,12 +1113,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131328399</v>
+        <v>131328388</v>
       </c>
       <c r="B7" t="n">
-        <v>91852</v>
+        <v>57902</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,30 +1271,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560809</v>
+        <v>560937</v>
       </c>
       <c r="R7" t="n">
-        <v>6913541</v>
+        <v>6913518</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1326,7 +1338,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1336,7 +1348,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påtagligt äldre bohål av sannolikt tretåig hackspett. Hålet sitter i en död gran omkring 1,5 meter ovan mark och innerdiametern är 4,5 cm. I området finns ett stort antal barrträd med ringhack i en för arten lämplig biotop.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,10 +1380,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131328388</v>
+        <v>131328399</v>
       </c>
       <c r="B8" t="n">
-        <v>57902</v>
+        <v>91852</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,42 +1391,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560937</v>
+        <v>560809</v>
       </c>
       <c r="R8" t="n">
-        <v>6913518</v>
+        <v>6913541</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,12 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Påtagligt äldre bohål av sannolikt tretåig hackspett. Hålet sitter i en död gran omkring 1,5 meter ovan mark och innerdiametern är 4,5 cm. I området finns ett stort antal barrträd med ringhack i en för arten lämplig biotop.</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1590,7 +1590,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131328393</v>
+        <v>131328394</v>
       </c>
       <c r="B10" t="n">
         <v>57902</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560855</v>
+        <v>560867</v>
       </c>
       <c r="R10" t="n">
-        <v>6913506</v>
+        <v>6913516</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1710,7 +1710,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131328394</v>
+        <v>131328393</v>
       </c>
       <c r="B11" t="n">
         <v>57902</v>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>560867</v>
+        <v>560855</v>
       </c>
       <c r="R11" t="n">
-        <v>6913516</v>
+        <v>6913506</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2284,7 +2284,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131328386</v>
+        <v>131328391</v>
       </c>
       <c r="B16" t="n">
         <v>57902</v>
@@ -2327,10 +2327,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560936</v>
+        <v>560893</v>
       </c>
       <c r="R16" t="n">
-        <v>6913562</v>
+        <v>6913550</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2524,7 +2524,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131328391</v>
+        <v>131328386</v>
       </c>
       <c r="B18" t="n">
         <v>57902</v>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560893</v>
+        <v>560936</v>
       </c>
       <c r="R18" t="n">
-        <v>6913550</v>
+        <v>6913562</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2612,12 +2612,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 26012-2024 artfynd.xlsx
+++ b/artfynd/A 26012-2024 artfynd.xlsx
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131328402</v>
+        <v>131328390</v>
       </c>
       <c r="B4" t="n">
         <v>57902</v>
@@ -925,12 +925,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -940,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560775</v>
+        <v>560915</v>
       </c>
       <c r="R4" t="n">
-        <v>6913519</v>
+        <v>6913505</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -985,12 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131328390</v>
+        <v>131328402</v>
       </c>
       <c r="B5" t="n">
         <v>57902</v>
@@ -1045,20 +1048,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1068,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560915</v>
+        <v>560775</v>
       </c>
       <c r="R5" t="n">
-        <v>6913505</v>
+        <v>6913519</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1113,7 +1108,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131328388</v>
+        <v>131328399</v>
       </c>
       <c r="B7" t="n">
-        <v>57902</v>
+        <v>91852</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,42 +1271,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560937</v>
+        <v>560809</v>
       </c>
       <c r="R7" t="n">
-        <v>6913518</v>
+        <v>6913541</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,7 +1326,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,12 +1336,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Påtagligt äldre bohål av sannolikt tretåig hackspett. Hålet sitter i en död gran omkring 1,5 meter ovan mark och innerdiametern är 4,5 cm. I området finns ett stort antal barrträd med ringhack i en för arten lämplig biotop.</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131328399</v>
+        <v>131328388</v>
       </c>
       <c r="B8" t="n">
-        <v>91852</v>
+        <v>57902</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1391,30 +1374,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getingtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560809</v>
+        <v>560937</v>
       </c>
       <c r="R8" t="n">
-        <v>6913541</v>
+        <v>6913518</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1446,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1451,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påtagligt äldre bohål av sannolikt tretåig hackspett. Hålet sitter i en död gran omkring 1,5 meter ovan mark och innerdiametern är 4,5 cm. I området finns ett stort antal barrträd med ringhack i en för arten lämplig biotop.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1590,7 +1590,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131328394</v>
+        <v>131328393</v>
       </c>
       <c r="B10" t="n">
         <v>57902</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560867</v>
+        <v>560855</v>
       </c>
       <c r="R10" t="n">
-        <v>6913516</v>
+        <v>6913506</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1710,7 +1710,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131328393</v>
+        <v>131328394</v>
       </c>
       <c r="B11" t="n">
         <v>57902</v>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>560855</v>
+        <v>560867</v>
       </c>
       <c r="R11" t="n">
-        <v>6913506</v>
+        <v>6913516</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2284,7 +2284,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131328391</v>
+        <v>131328386</v>
       </c>
       <c r="B16" t="n">
         <v>57902</v>
@@ -2327,10 +2327,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560893</v>
+        <v>560936</v>
       </c>
       <c r="R16" t="n">
-        <v>6913550</v>
+        <v>6913562</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2524,7 +2524,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131328386</v>
+        <v>131328391</v>
       </c>
       <c r="B18" t="n">
         <v>57902</v>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560936</v>
+        <v>560893</v>
       </c>
       <c r="R18" t="n">
-        <v>6913562</v>
+        <v>6913550</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2612,12 +2612,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 26012-2024 artfynd.xlsx
+++ b/artfynd/A 26012-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131328398</v>
       </c>
       <c r="B2" t="n">
-        <v>92131</v>
+        <v>92137</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131328384</v>
       </c>
       <c r="B3" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>131328390</v>
       </c>
       <c r="B4" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>131328402</v>
       </c>
       <c r="B5" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>131328387</v>
       </c>
       <c r="B6" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>131328399</v>
       </c>
       <c r="B7" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>131328388</v>
       </c>
       <c r="B8" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>131328396</v>
       </c>
       <c r="B9" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>131328393</v>
       </c>
       <c r="B10" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>131328394</v>
       </c>
       <c r="B11" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>131328397</v>
       </c>
       <c r="B12" t="n">
-        <v>92292</v>
+        <v>92298</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>131328401</v>
       </c>
       <c r="B13" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>131328389</v>
       </c>
       <c r="B14" t="n">
-        <v>92131</v>
+        <v>92137</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>131328400</v>
       </c>
       <c r="B15" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131328386</v>
+        <v>131328395</v>
       </c>
       <c r="B16" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2327,10 +2327,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560936</v>
+        <v>560835</v>
       </c>
       <c r="R16" t="n">
-        <v>6913562</v>
+        <v>6913527</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2404,10 +2404,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131328395</v>
+        <v>131328386</v>
       </c>
       <c r="B17" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560835</v>
+        <v>560936</v>
       </c>
       <c r="R17" t="n">
-        <v>6913527</v>
+        <v>6913562</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2527,7 +2527,7 @@
         <v>131328391</v>
       </c>
       <c r="B18" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>131328392</v>
       </c>
       <c r="B19" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>131328385</v>
       </c>
       <c r="B20" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 26012-2024 artfynd.xlsx
+++ b/artfynd/A 26012-2024 artfynd.xlsx
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131328390</v>
+        <v>131328402</v>
       </c>
       <c r="B4" t="n">
         <v>57904</v>
@@ -925,20 +925,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -948,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560915</v>
+        <v>560775</v>
       </c>
       <c r="R4" t="n">
-        <v>6913505</v>
+        <v>6913519</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +975,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +985,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,7 +1017,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131328402</v>
+        <v>131328390</v>
       </c>
       <c r="B5" t="n">
         <v>57904</v>
@@ -1048,12 +1045,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1063,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560775</v>
+        <v>560915</v>
       </c>
       <c r="R5" t="n">
-        <v>6913519</v>
+        <v>6913505</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1103,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,12 +1113,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 26012-2024 artfynd.xlsx
+++ b/artfynd/A 26012-2024 artfynd.xlsx
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131328402</v>
+        <v>131328390</v>
       </c>
       <c r="B4" t="n">
         <v>57904</v>
@@ -925,12 +925,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -940,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560775</v>
+        <v>560915</v>
       </c>
       <c r="R4" t="n">
-        <v>6913519</v>
+        <v>6913505</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -985,12 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131328390</v>
+        <v>131328402</v>
       </c>
       <c r="B5" t="n">
         <v>57904</v>
@@ -1045,20 +1048,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1068,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560915</v>
+        <v>560775</v>
       </c>
       <c r="R5" t="n">
-        <v>6913505</v>
+        <v>6913519</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1113,7 +1108,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
